--- a/planos_empresas/plano_empresa_00995.xlsx
+++ b/planos_empresas/plano_empresa_00995.xlsx
@@ -413,9 +413,235 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>010301 - Processamento de dados, textos, imagens, vídeos, páginas eletrônicas, aplicativos e sistemas de info</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr"/>
+      <c r="D1" t="inlineStr"/>
+      <c r="E1" t="inlineStr"/>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>070201 - Execução, por administração, de obras de construção civil, hidráulica ou elétrica e de outras obras semelhantes, inclusive sondagem, perfuração de poços, escavação, drenagem e irrigação, terraplanagem, pavimentação, concretagem e a instalação e montagem de produtos, peças e equipamentos (exceto o fornecimento de mercadorias produzidas pelo prestador de serviços fora do local da prestação dos serviços, que fica sujeito ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>070602 - Colocação e instalação de assoalhos, revestimentos de parede, vidros, divisórias, placas de gesso e congêneres, com material fornecido pelo tomador do serviço.</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>110402 - Carga, descarga, arrumação de bens de qualquer espécie.</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>130501 - Composição gráfica, inclusive confecção de impressos gráficos, fotocomposição, clicheria, zincografia, litografia e fotolitografia, exceto se destinados a posterior operação de comercialização ou industrialização, ainda que incorporados, de qualquer forma, a outra mercadoria que deva ser objeto de posterior circulação, tais como bulas, rótulos, etiquetas, caixas, cartuchos, embalagens e manuais técnicos e de instrução, quando ficarão sujeitos ao ICMS.</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>140101 - Lubrificação, limpeza, lustração, revisão, carga e recarga, conserto, restauração, blindagem, manutenção e conservação de máquinas, veículos, aparelhos, equipamentos, motores, elevadores ou de qualquer objeto (exceto peças e partes empregadas, que ficam sujeitas ao ICMS).</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>140501 - Restauração, recondicionamento, acondicionamento, pintura, beneficiamento, lavagem, secagem, tingimento, galvanoplastia, anodização, corte, recorte, plastificação, costura, acabamento, polimento e congêneres de objetos quaisquer.</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>140601 - Instalação e montagem de aparelhos, máquinas e equipamentos, inclusive montagem industrial, prestados ao usuário final, exclusivamente com material por ele fornecido.</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>160201 - Outros serviços de transporte de natureza municipal.</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>170901 - Perícias, laudos, exames técnicos e análises técnicas.</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>171201 - Administração em geral, inclusive de bens e negócios de terceiros.</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>171401 - Advocacia</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>171901 - Contabilidade, inclusive serviços técnicos e auxiliares.</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3339</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>240101 - Serviços de chaveiros, confecção de carimbos e congêneres.</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>260101 - Serviços de coleta, remessa ou entrega de correspondências, documentos, objetos, bens ou valores, inclusive pelos correios e suas agências franqueadas.</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>2135</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>